--- a/Collections/EURO/Ireland/#EURO#Ireland#Commemorative#[2007-present]#UNC.xlsx
+++ b/Collections/EURO/Ireland/#EURO#Ireland#Commemorative#[2007-present]#UNC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Ireland\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF52E57A-60F6-4E3F-9079-A9842F814996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B48826-86F2-4BDF-8E40-6DFE56A3EAEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -78,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="46">
   <si>
     <t>Year</t>
   </si>
@@ -486,7 +489,15 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="16">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -613,9 +624,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="2" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -884,7 +895,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="13" customWidth="1"/>
@@ -1420,6 +1431,33 @@
         <v/>
       </c>
     </row>
+    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="11" t="str">
+        <f t="shared" ref="H21" si="4">IF(OR(AND(G21&gt;1,G21&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B2:F2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="2">
@@ -1427,11 +1465,26 @@
     <mergeCell ref="C1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="G3 G15 G11:G12 G8 G5">
+    <cfRule type="containsText" dxfId="15" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3 G15 G11:G12 G8 G5">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G13">
     <cfRule type="containsText" dxfId="14" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G15 G3 G11:G12 G8 G5">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G13))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1443,9 +1496,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G13">
+  <conditionalFormatting sqref="G14">
     <cfRule type="containsText" dxfId="13" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G13))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G14))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="28">
       <colorScale>
@@ -1458,9 +1511,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G14">
+  <conditionalFormatting sqref="G10">
     <cfRule type="containsText" dxfId="12" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G14))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G10))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="26">
       <colorScale>
@@ -1473,9 +1526,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G10">
+  <conditionalFormatting sqref="G9">
     <cfRule type="containsText" dxfId="11" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G10))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G9))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="24">
       <colorScale>
@@ -1488,9 +1541,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G9">
+  <conditionalFormatting sqref="G7">
     <cfRule type="containsText" dxfId="10" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G9))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G7))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="22">
       <colorScale>
@@ -1503,9 +1556,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G7">
+  <conditionalFormatting sqref="G6">
     <cfRule type="containsText" dxfId="9" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G7))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G6))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="20">
       <colorScale>
@@ -1518,9 +1571,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G6">
+  <conditionalFormatting sqref="G4">
     <cfRule type="containsText" dxfId="8" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G6))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="18">
       <colorScale>
@@ -1533,9 +1586,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4">
+  <conditionalFormatting sqref="G16:G17">
     <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G16))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="16">
       <colorScale>
@@ -1548,11 +1601,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G16:G17">
-    <cfRule type="containsText" dxfId="6" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G16))))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="14">
+  <conditionalFormatting sqref="G18">
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G18">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -1563,12 +1618,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G18">
+  <conditionalFormatting sqref="G19">
     <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G18))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G19))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G18">
+  <conditionalFormatting sqref="G19">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1580,12 +1635,10 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G19">
+  <conditionalFormatting sqref="G20">
     <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G19))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G19">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1597,9 +1650,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G20">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
+  <conditionalFormatting sqref="G21">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
